--- a/data/output/evaluasi_33.xlsx
+++ b/data/output/evaluasi_33.xlsx
@@ -8,15 +8,40 @@
   </bookViews>
   <sheets>
     <sheet name="3300" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="3313" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="3327" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="3375" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="3304" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="3306" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="3320" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="3312" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="3314" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="3329" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="3303" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="3305" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="3307" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="3308" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="3314" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="3317" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="3325" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="3374" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="3313" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="3309" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="3316" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="3323" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="3328" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="3329" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="3375" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="3315" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="3321" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="3326" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="3373" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="3301" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="3302" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="3306" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="3322" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="3372" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="3310" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="3312" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="3320" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="3324" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="3327" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="3376" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet name="3311" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet name="3319" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet name="3371" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet name="3304" sheetId="35" state="visible" r:id="rId35"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -434,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,20 +505,20 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>12.9981919738036</v>
+        <v>-7.050901595922945</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>adhb_net_ekspor_q1-25</t>
+          <t>adhb_pkp_q3-25</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Diskrepansi lebih dari +- 5 persen</t>
+          <t>Diskrepansi ADHB antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -508,20 +533,20 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q2-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1091.031713613718</v>
+        <v>-8.883507808423236</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>adhb_net_ekspor_q2-25</t>
+          <t>adhb_pi_q3-25</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Diskrepansi lebih dari +- 5 persen</t>
+          <t>Diskrepansi ADHB antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -536,20 +561,20 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q2-25</t>
+          <t>q1-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.02458623108875059</v>
+        <v>10.61433001258184</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>distribusi_net_ekspor_q2-25 vs distribusi_net_ekspor_q2-25.1</t>
+          <t>adhb_net_ekspor_q1-25</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Distribusi lebih dari +- 20 persen</t>
+          <t>Diskrepansi ADHB antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -568,16 +593,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.295873421791815</v>
+        <v>40.00205901524738</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pkp_q2-25 vs implisit_q-to-q_pkp_q2-25.1</t>
+          <t>adhb_net_ekspor_q2-25</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Growth berlawanan arah</t>
+          <t>Diskrepansi ADHB antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -592,20 +617,608 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-143.4854076136543</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>adhb_net_ekspor_q3-25</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Diskrepansi ADHB antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>33</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Jawa Tengah</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-12.5481415503753</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>adhk_pkp_q3-25</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Diskrepansi ADHK antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>33</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Jawa Tengah</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>17.37756103523434</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>adhk_net_ekspor_q3-25</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Diskrepansi ADHK antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>33</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Jawa Tengah</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.187373404816787</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q3-25 vs q-to-q_pkrt_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Nilai antara Provinsi dan total Kabupaten/Kota beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>33</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Jawa Tengah</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>6.716346305213926</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25 vs q-to-q_pkp_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Nilai antara Provinsi dan total Kabupaten/Kota beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>33</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Jawa Tengah</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-8.629922183947022</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q1-25 vs q-to-q_pmtb_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>33</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Jawa Tengah</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>5.366727657209823</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q3-25 vs q-to-q_pmtb_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>33</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Jawa Tengah</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>4.899402060200331</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q3-25 vs y-on-y_pdrb_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,01 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>33</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Jawa Tengah</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>4.057293649610102</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>y-on-y_pkrt_q3-25 vs y-on-y_pkrt_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>33</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Jawa Tengah</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>-2.214220201710087</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q1-25 vs y-on-y_pkp_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>33</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Jawa Tengah</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>19.42582795468011</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25 vs y-on-y_pkp_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>33</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Jawa Tengah</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>3.114437821692351</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q1-25 vs y-on-y_pmtb_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>33</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Jawa Tengah</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>7.446078786479965</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25 vs y-on-y_pmtb_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>33</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Jawa Tengah</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>-2.214220201710087</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q1-25 vs c-to-c_pkp_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>33</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Jawa Tengah</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>4.966202047319297</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25 vs c-to-c_pkp_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>33</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Jawa Tengah</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>3.114437821692351</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q1-25 vs c-to-c_pmtb_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>33</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Jawa Tengah</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
           <t>q2-25</t>
         </is>
       </c>
-      <c r="D6" t="n">
-        <v>-0.0677530801275671</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>implisit_y-on-y_pkp_q2-25 vs implisit_y-on-y_pkp_q2-25.1</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Growth berlawanan arah</t>
+      <c r="D22" t="n">
+        <v>5.413932216682198</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q2-25 vs c-to-c_pmtb_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>33</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Jawa Tengah</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>-0.5752625276726278</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q3-25 vs implisit_q-to-q_pkrt_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Nilai antara Provinsi dan total Kabupaten/Kota beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>33</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Jawa Tengah</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>-2.390961422152074</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q3-25 vs implisit_q-to-q_pklnprt_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Nilai antara Provinsi dan total Kabupaten/Kota beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>33</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Jawa Tengah</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>-5.849207560309292</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q3-25 vs implisit_q-to-q_pkp_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>33</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Jawa Tengah</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>-0.357054722929678</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_q3-25 vs implisit_y-on-y_pklnprt_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Nilai antara Provinsi dan total Kabupaten/Kota beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>33</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Jawa Tengah</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>-5.198361164589299</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q3-25 vs implisit_y-on-y_pkp_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Nilai antara Provinsi dan total Kabupaten/Kota beda arah</t>
         </is>
       </c>
     </row>
@@ -620,7 +1233,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -657,6 +1270,1216 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
+        <v>3313</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Karanganyar</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-2.824450846128364</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q1-25_ril vs sog_y-on-y_pi_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3313</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Karanganyar</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-2.789510159667441</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q2-25_ril vs sog_y-on-y_pi_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3313</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Karanganyar</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.9691926485270799</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3313</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Karanganyar</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>7.300767977043004</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3313</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Karanganyar</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-1.29513045407698</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3313</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Karanganyar</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-2.883528678835074</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3309</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Boyolali</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-1.245351284410449</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3309</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Boyolali</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>14.51144672968554</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3309</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Boyolali</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.2021193400950592</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q3-25_prov vs implisit_q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3309</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Boyolali</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.4569954887711724</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q3-25_prov vs implisit_y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3316</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Blora</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-1.750535496030225</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3316</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Blora</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.5288475443469332</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q3-25_prov vs q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3316</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Blora</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.370628519591407</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3316</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Blora</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0.4173408317244611</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3316</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Blora</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>12.22657693474974</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3316</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Blora</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>2.41200174543379</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3316</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Blora</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.5923932780087702</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q3-25_prov vs implisit_y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3323</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Temanggung</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-2.343622707016609</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3323</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Temanggung</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-1.556274846338726</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3323</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Temanggung</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.0248136722532774</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q3-25_prov vs implisit_q-to-q_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3323</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Temanggung</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.1170186202114714</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q3-25_prov vs implisit_y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3328</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Tegal</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.8916310619928296</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3328</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Tegal</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-7.772646323220171</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q3-25_prov vs q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3328</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Tegal</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-1.607591132885671</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3328</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Tegal</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>30.41723316060012</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3328</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Tegal</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1.346316140087047</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3328</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Tegal</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-4.888582595370608</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pkrt_q3-25_prov vs y-on-y_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3328</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Tegal</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.2242124143906324</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>3328</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Tegal</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>48.89851434315595</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>3328</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Tegal</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>2.664240512446329</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>3328</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Tegal</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>14.69442372624234</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>3328</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Tegal</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-3.456655996592012</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q3-25_prov vs implisit_q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3328</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Tegal</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-0.09745527434811976</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q3-25_prov vs implisit_q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>3328</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Tegal</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>-2.752843667481147</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q3-25_prov vs implisit_y-on-y_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>3328</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Tegal</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>-1.960587595759084</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q3-25_prov vs implisit_y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
         <v>3329</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -666,20 +2489,1296 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.02718119963392249</v>
+        <v>-3.47097229559572</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pkrt_q1-25_ril vs implisit_q-to-q_pkrt_q1-25_rev</t>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3329</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Brebes</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.0376727647418118</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q3-25_prov vs q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3329</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Brebes</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>30.03385078675201</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3329</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Brebes</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>44.33903583868785</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3329</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Brebes</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1.088219223025838</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q3-25_prov vs y-on-y_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3329</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Brebes</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>44.07751393590687</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3329</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Brebes</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>43.47624482903198</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>3329</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Brebes</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>13.9684659207929</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>3329</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Brebes</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>16.14683183098169</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>3329</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Brebes</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-1.934469243658815</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q3-25_prov vs implisit_q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>3329</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Brebes</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-0.6868050407872091</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q3-25_prov vs implisit_y-on-y_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3329</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Brebes</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-0.3697347346168225</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pmtb_q3-25_prov vs implisit_y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3375</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kota Pekalongan</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-1.4375693352695</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3375</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kota Pekalongan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0.1945224053784536</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3375</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kota Pekalongan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>11.44931323228729</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3375</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kota Pekalongan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.9167539306994068</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q3-25_prov vs implisit_q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3375</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kota Pekalongan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.3058853537485896</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q3-25_prov vs implisit_q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3375</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kota Pekalongan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-2.717583264784953</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q3-25_prov vs implisit_y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3375</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kota Pekalongan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-2.326938370535237</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>3375</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kota Pekalongan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-2.998605044755158</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3315</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Grobogan</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-1.982148898409314</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q3-25_prov vs q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3315</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Grobogan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-6.247812792081209</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3315</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Grobogan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>301.3926220078718</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3315</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Grobogan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>19.29943516448725</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3315</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Grobogan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-2.675787942415988</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3315</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Grobogan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>298.2131179922327</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3315</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Grobogan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>25.28963872513323</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>3315</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Grobogan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>102.3106512790476</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>3315</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Grobogan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>14.00606017410318</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>3315</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Grobogan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-1.447612230189703</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q3-25_prov vs implisit_q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>3315</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Grobogan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-66.99905359309268</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q3-25_prov vs implisit_q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3315</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Grobogan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-0.4089953682938349</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkrt_q3-25_prov vs implisit_y-on-y_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>3315</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Grobogan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>-66.55583412213733</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q3-25_prov vs implisit_y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3321</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Demak</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.357025242992921</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q3-25_prov vs q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3321</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Demak</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.2517198248573662</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q3-25_prov vs implisit_y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3326</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Pekalongan</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.1328557125858841</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q3-25_prov vs q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3326</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Pekalongan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.6848491026604995</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3326</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Pekalongan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>16.38203035302815</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3326</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Pekalongan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>4.493749982200741</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3326</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Pekalongan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.8188135291664801</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q3-25_prov vs implisit_q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -694,7 +3793,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -731,11 +3830,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3313</v>
+        <v>3303</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Karanganyar</t>
+          <t>Kabupaten Purbalingga</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -744,16 +3843,1876 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1422.68</v>
+        <v>3.932313314703979</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>adhb_pi_q1-25_ril vs adhb_pi_q1-25_rev</t>
+          <t>sog_q_pi_q1-25_ril vs sog_q_pi_q1-25_rev</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3303</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Purbalingga</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-3.482621904642175</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q1-25_ril vs sog_y-on-y_pi_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3303</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Purbalingga</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-3.593496855021818</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q2-25_ril vs sog_y-on-y_pi_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3303</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Purbalingga</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-2.185982243751755</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3303</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Purbalingga</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-1.488618846272966</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q3-25_prov vs implisit_y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3303</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Purbalingga</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-4.153139579360501</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3373</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kota Salatiga</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.2216322692387284</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q3-25_prov vs q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3373</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kota Salatiga</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>6.332791840523151</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3373</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kota Salatiga</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>11.51452204343357</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3373</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kota Salatiga</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-5.217474229983969</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3373</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kota Salatiga</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-3.129886660662628</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3373</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kota Salatiga</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.4119490346194002</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q3-25_prov vs implisit_q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3301</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Cilacap</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.04690219095038405</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3301</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Cilacap</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.09054603586333117</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3301</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Cilacap</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.9252480006151002</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3301</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Cilacap</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.7524508227881828</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q3-25_prov vs implisit_q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3301</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Cilacap</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.3161992286199524</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q3-25_prov vs implisit_y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3302</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Banyumas</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-1.27978693214743</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3302</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Banyumas</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>2.175755075292416</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3302</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Banyumas</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-1.794726068679281</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3306</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Purworejo</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-1.465991086306936</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3306</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Purworejo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>1.569538233621534</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3306</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Purworejo</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.7518298796170566</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3322</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Semarang</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.0179193677545263</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3322</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Semarang</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0.5802495581176708</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3322</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Semarang</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.05374125429254768</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3322</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Semarang</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-5.319036622787831</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q3-25_prov vs implisit_q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3322</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Semarang</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-3.78011001894771</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q3-25_prov vs implisit_y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3372</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kota Surakarta</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.5035067056617925</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3372</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kota Surakarta</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>9.854081767671921</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3372</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kota Surakarta</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>1.796376921082588</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3372</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kota Surakarta</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1.148642438381487</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3310</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Klaten</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>3.911382691597285</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3310</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Klaten</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>32.6489602816615</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3310</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Klaten</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-11.85137662585277</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3310</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Klaten</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>10.14112322409968</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3310</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Klaten</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-6.332728059486121</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3312</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Wonogiri</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>19.29171814342186</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3312</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Wonogiri</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>30.88281862743291</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3312</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Wonogiri</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>9.481181434109823</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3312</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Wonogiri</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.07077130650382636</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q3-25_prov vs implisit_q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3312</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Wonogiri</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-1.890247646732754</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q3-25_prov vs implisit_y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3320</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Jepara</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>3.992138320580226</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3320</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Jepara</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>25.20553158750299</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3320</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Jepara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>14.53154345430656</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3320</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Jepara</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>8.052114128075923</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3324</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Kendal</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>35.85591870939688</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3324</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Kendal</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>44.9456207327594</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3324</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Kendal</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>18.13607608029529</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3324</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Kendal</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>12.4035643393243</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3324</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Kendal</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>14.80270470220041</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -805,6 +5764,80 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
+        <v>3305</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Kebumen</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>2.721588970111104</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q1-25_ril vs sog_q_pi_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
         <v>3327</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -814,20 +5847,894 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-102718.299999998</v>
+        <v>25.27261874653301</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>adhb_net_ekspor_q1-25_ril vs adhb_net_ekspor_q1-25_rev</t>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3327</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Pemalang</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>19.07384410262663</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3376</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kota Tegal</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>1.296126788127874</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3376</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kota Tegal</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>2.286529758198173</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3376</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kota Tegal</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>10.30766996871963</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3376</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kota Tegal</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0.7638942607842624</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3376</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kota Tegal</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>2.176411516870566</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3376</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kota Tegal</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-2.771075524383297</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q3-25_prov vs implisit_y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3311</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Sukoharjo</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0.9228312288647459</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3311</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Sukoharjo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>2.232444230363678</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3311</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Sukoharjo</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.5470080998198763</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3319</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Kudus</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-9.214536704479537</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3319</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Kudus</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>13.60188846009846</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3319</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Kudus</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-4.15056236841947</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3319</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Kudus</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0.1385813883288857</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>c-to-c_pdrb_q3-25_prov vs c-to-c_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3319</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Kudus</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>5.197923527374877</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3319</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Kudus</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.1135067401166098</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q3-25_prov vs implisit_q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3319</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Kudus</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.06474816455393587</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q3-25_prov vs implisit_q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>3319</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Kudus</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.8940072511204645</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q3-25_prov vs implisit_y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3371</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kota Magelang</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-1.579187673799823</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3371</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kota Magelang</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.04096462216633195</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q3-25_prov vs implisit_q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3371</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kota Magelang</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.001869269089481365</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q3-25_prov vs implisit_y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3304</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Banjarnegara</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.05503346053951535</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q3-25_prov vs implisit_q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3304</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Banjarnegara</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.04966332113444411</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q3-25_prov vs implisit_q-to-q_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -842,7 +6749,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -879,11 +6786,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3375</v>
+        <v>3307</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kota Pekalongan</t>
+          <t>Kabupaten Wonosobo</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -892,44 +6799,128 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-201.108101039251</v>
+        <v>2.424760541735337</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>adhk_pi_q1-25_ril vs adhk_pi_q1-25_rev</t>
+          <t>sog_q_pi_q1-25_ril vs sog_q_pi_q1-25_rev</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>3375</v>
+        <v>3307</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kota Pekalongan</t>
+          <t>Kabupaten Wonosobo</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.0008236821976075538</v>
+        <v>-0.03102678673404339</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>sog_q_pi_q1-25_ril vs sog_q_pi_q1-25_rev</t>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3307</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Wonosobo</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.08895417292282937</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q3-25_prov vs q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3307</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Wonosobo</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.04307633693080501</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q3-25_prov vs implisit_q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3307</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Wonosobo</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.03724327408138831</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q3-25_prov vs implisit_q-to-q_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -944,7 +6935,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -981,11 +6972,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3304</v>
+        <v>3308</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Banjarnegara</t>
+          <t>Kabupaten Magelang</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -994,128 +6985,296 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>14179.3500000005</v>
+        <v>2.783360197777573</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>adhk_net_ekspor_q1-25_ril vs adhk_net_ekspor_q1-25_rev</t>
+          <t>sog_q_pi_q1-25_ril vs sog_q_pi_q1-25_rev</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>3304</v>
+        <v>3308</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kabupaten Banjarnegara</t>
+          <t>Kabupaten Magelang</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.05020889462876608</v>
+        <v>-12.05123013441682</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>y-on-y_pkp_q1-25_ril vs y-on-y_pkp_q1-25_rev</t>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3304</v>
+        <v>3308</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kabupaten Banjarnegara</t>
+          <t>Kabupaten Magelang</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.05020889462876608</v>
+        <v>-8.906890522890871</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>c-to-c_pkp_q1-25_ril vs c-to-c_pkp_q1-25_rev</t>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>3304</v>
+        <v>3308</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kabupaten Banjarnegara</t>
+          <t>Kabupaten Magelang</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.3101583827330032</v>
+        <v>-5.834717831259111</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>implisit_y-on-y_pkp_q1-25_ril vs implisit_y-on-y_pkp_q1-25_rev</t>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>3304</v>
+        <v>3308</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kabupaten Banjarnegara</t>
+          <t>Kabupaten Magelang</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.002354880335523533</v>
+        <v>-30.5948157664529</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>sog_y-on-y_pkp_q1-25_ril vs sog_y-on-y_pkp_q1-25_rev</t>
+          <t>implisit_q-to-q_pkrt_q3-25_prov vs implisit_q-to-q_pkrt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3308</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Magelang</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-65.77481126641318</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q3-25_prov vs implisit_q-to-q_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3308</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Magelang</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>39.37671699046775</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q3-25_prov vs implisit_q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>3308</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Magelang</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.2627659643565064</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q3-25_prov vs implisit_q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>3308</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Magelang</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-30.03768342845926</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkrt_q3-25_prov vs implisit_y-on-y_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>3308</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Magelang</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-65.09278057763549</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_q3-25_prov vs implisit_y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>3308</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Magelang</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>39.86161283793701</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q3-25_prov vs implisit_y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -1130,7 +7289,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1167,11 +7326,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3306</v>
+        <v>3314</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Purworejo</t>
+          <t>Kabupaten Sragen</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1180,72 +7339,156 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.03646704138328762</v>
+        <v>2.900508848860841</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>y-on-y_pkp_q1-25_ril vs y-on-y_pkp_q1-25_rev</t>
+          <t>sog_q_pi_q1-25_ril vs sog_q_pi_q1-25_rev</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Growth revisi berlawanan arah</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>3306</v>
+        <v>3314</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kabupaten Purworejo</t>
+          <t>Kabupaten Sragen</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.03646704138328762</v>
+        <v>-0.4400507566951857</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>c-to-c_pkp_q1-25_ril vs c-to-c_pkp_q1-25_rev</t>
+          <t>q-to-q_pkrt_q3-25_prov vs q-to-q_pkrt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Growth revisi berlawanan arah</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3306</v>
+        <v>3314</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kabupaten Purworejo</t>
+          <t>Kabupaten Sragen</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.002226495153210881</v>
+        <v>-17.32315101516926</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>sog_y-on-y_pkp_q1-25_ril vs sog_y-on-y_pkp_q1-25_rev</t>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Growth revisi berlawanan arah</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3314</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Sragen</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-8.539990106477033</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3314</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Sragen</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-4.353068645931544</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3314</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Sragen</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>2.028514602218479</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q3-25_prov vs implisit_q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1260,7 +7503,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1297,11 +7540,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3320</v>
+        <v>3317</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Jepara</t>
+          <t>Kabupaten Rembang</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1310,72 +7553,100 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.04479069948711098</v>
+        <v>5.737407658257701</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>y-on-y_pkp_q1-25_ril vs y-on-y_pkp_q1-25_rev</t>
+          <t>sog_q_pi_q1-25_ril vs sog_q_pi_q1-25_rev</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>3320</v>
+        <v>3317</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kabupaten Jepara</t>
+          <t>Kabupaten Rembang</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.04479069948711098</v>
+        <v>-0.5608883952500637</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>c-to-c_pkp_q1-25_ril vs c-to-c_pkp_q1-25_rev</t>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3320</v>
+        <v>3317</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kabupaten Jepara</t>
+          <t>Kabupaten Rembang</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.002175829680490557</v>
+        <v>13.23137400009091</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>sog_y-on-y_pkp_q1-25_ril vs sog_y-on-y_pkp_q1-25_rev</t>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3317</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Rembang</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>4.315261508744539</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -1390,7 +7661,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1427,11 +7698,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3312</v>
+        <v>3325</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Wonogiri</t>
+          <t>Kabupaten Batang</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1440,16 +7711,100 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.1928854516483473</v>
+        <v>2.211818953708407</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pkrt_q1-25_ril vs implisit_q-to-q_pkrt_q1-25_rev</t>
+          <t>sog_q_pi_q1-25_ril vs sog_q_pi_q1-25_rev</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3325</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Batang</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>2.535107794184433</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3325</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Batang</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>15.41783302837268</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3325</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Batang</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>12.92047891336984</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -1464,7 +7819,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1501,11 +7856,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3314</v>
+        <v>3374</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Sragen</t>
+          <t>Kota Semarang</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1514,16 +7869,44 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.08046968091846868</v>
+        <v>2.714620875107708</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pkrt_q1-25_ril vs implisit_q-to-q_pkrt_q1-25_rev</t>
+          <t>sog_q_pi_q1-25_ril vs sog_q_pi_q1-25_rev</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3374</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kota Semarang</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>9.554483929012271</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>

--- a/data/output/evaluasi_33.xlsx
+++ b/data/output/evaluasi_33.xlsx
@@ -770,7 +770,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -854,7 +854,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -882,7 +882,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -938,7 +938,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -966,7 +966,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -994,7 +994,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1050,7 +1050,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
